--- a/stories/arbres/ATOM-EMO.LEX.005-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo construit une tour de cubes. Il est dans le salon, avec papa. Son frère Nino prend le cube du haut. La tour tombe sur le tapis. Hugo sent son visage chaud. Son ventre est dur. Hugo dit : je suis en colère. Il ouvre les doigts. Ses mains restent loin de Nino. Hugo fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers papa. Papa est l'adulte dans le salon. Hugo dit : papa, je suis en colère. Papa écoute. Plus tard, ils reconstruiront. La colère a un nom. Les mains restent loin.</t>
+          <t>Hugo construit une tour de cubes. Il est dans le salon, avec papa. Son frère Nino prend le cube du haut. La tour tombe sur le tapis. Hugo sent son visage chaud. Son ventre est dur. Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Nino. Hugo fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers papa. Papa est l'adulte dans le salon. Papa, je suis en colère. Papa écoute. Plus tard, ils reconstruiront. La colère a un nom. Les mains restent loin.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,15 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo construit une tour de cubes. Il est dans le salon, avec papa. Son frère Nino prend le cube du haut. La tour tombe sur le tapis. Hugo sent son visage chaud. Son ventre est dur.
+enfant-m|Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Nino.
+narrateur|Hugo fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers papa. Papa est l'adulte dans le salon.
+enfant-m|Papa, je suis en colère. Papa écoute. Plus tard, ils reconstruiront.
+narrateur|La colère a un nom. Les mains restent loin.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1494,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo est en colère. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1667,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers papa, l'adulte.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1830,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hugo s'assoit près de papa. Les cubes restent sur le tapis.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1997,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2037,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-01.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1314,6 +1319,7 @@
 narrateur|La colère a un nom. Les mains restent loin.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Hugo est en colère. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1672,6 +1679,7 @@
           <t>narrateur|Hugo a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers papa, l'adulte.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1835,6 +1843,7 @@
           <t>narrateur|Hugo s'assoit près de papa. Les cubes restent sur le tapis.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2002,6 +2011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2030,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2044,6 +2054,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2245,6 +2269,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.005-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-01.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Être en colère</t>
+          <t>Amir et la tour de cubes</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>La tour d'Amir tombe. Il nomme sa colère. Mains loin. Il s'éloigne. Il va vers papa.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugo construit une tour de cubes. Il est dans le salon, avec papa. Son frère Nino prend le cube du haut. La tour tombe sur le tapis. Hugo sent son visage chaud. Son ventre est dur. Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Nino. Hugo fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers papa. Papa est l'adulte dans le salon. Papa, je suis en colère. Papa écoute. Plus tard, ils reconstruiront. La colère a un nom. Les mains restent loin.</t>
+          <t>La pluie tapote la vitre. Le tapis a des losanges bleus. Un panier de cubes attend. Les cubes sentent le bois. Le canapé est tout mou. Un cube jaune brille un peu. Une chaussette sèche près du radiateur. La pluie fait un petit bruit. Amir, tu prends le panier ? Oui. Je fais une tour. Nino s'assoit près du tapis. En ce moment, Amir construit une tour. La tour est haute. Nino prend le cube du haut. La tour tombe sur le tapis. Amir sent son visage chaud. Son ventre est dur. Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Nino. Les mains restent loin. Amir fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Tu as soufflé. Bravo. Tu peux venir vers moi. Amir va vers papa. Papa est l'adulte dans le salon. Papa, je suis en colère. Je t'écoute. La tour est tombée. Tu as nommé. Tes mains sont loin. Plus tard, on reconstruira. Nino pose le cube dans le panier. Le bois fait un petit bruit. Tu t'es éloigné. C'est bien. Les mains restent loin. On va vers un adulte. La colère a un nom. Les mains restent loin. La pluie tapote encore. Les losanges bleus restent calmes.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,14 +1324,56 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hugo construit une tour de cubes. Il est dans le salon, avec papa. Son frère Nino prend le cube du haut. La tour tombe sur le tapis. Hugo sent son visage chaud. Son ventre est dur.
-enfant-m|Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Nino.
-narrateur|Hugo fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers papa. Papa est l'adulte dans le salon.
-enfant-m|Papa, je suis en colère. Papa écoute. Plus tard, ils reconstruiront.
-narrateur|La colère a un nom. Les mains restent loin.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La pluie tapote la vitre.
+narrateur|Le tapis a des losanges bleus.
+narrateur|Un panier de cubes attend.
+narrateur|Les cubes sentent le bois.
+narrateur|Le canapé est tout mou.
+narrateur|Un cube jaune brille un peu.
+narrateur|Une chaussette sèche près du radiateur.
+maman|La pluie fait un petit bruit.
+papa|Amir, tu prends le panier ?
+enfant-m|Oui. Je fais une tour.
+narrateur|Nino s'assoit près du tapis.
+narrateur|En ce moment, Amir construit une tour.
+narrateur|La tour est haute.
+narrateur|Nino prend le cube du haut.
+narrateur|La tour tombe sur le tapis.
+narrateur|Amir sent son visage chaud.
+narrateur|Son ventre est dur.
+enfant-m|Je suis en colère.
+narrateur|Il ouvre les doigts.
+narrateur|Ses mains restent loin de Nino.
+papa|Les mains restent loin.
+narrateur|Amir fait un pas en arrière.
+narrateur|Il peut s'éloigner.
+narrateur|Il s'éloigne vers le canapé.
+narrateur|Il souffle trois fois.
+maman|Tu as soufflé. Bravo.
+papa|Tu peux venir vers moi.
+narrateur|Amir va vers papa.
+narrateur|Papa est l'adulte dans le salon.
+enfant-m|Papa, je suis en colère.
+papa|Je t'écoute.
+enfant-m|La tour est tombée.
+maman|Tu as nommé. Tes mains sont loin.
+papa|Plus tard, on reconstruira.
+narrateur|Nino pose le cube dans le panier.
+narrateur|Le bois fait un petit bruit.
+maman|Tu t'es éloigné. C'est bien.
+enfant-m|Les mains restent loin.
+papa|On va vers un adulte.
+narrateur|La colère a un nom.
+narrateur|Les mains restent loin.
+narrateur|La pluie tapote encore.
+narrateur|Les losanges bleus restent calmes.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>pluie,cubes</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1344,7 +1398,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hugo est en colère. Que fait-il ?</t>
+          <t>Amir est en colère. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1558,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Hugo est en colère. Que fait-il ?</t>
+          <t>narrateur|Amir est en colère.
+narrateur|Que fait-il ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugo a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers papa, l'adulte.</t>
+          <t>Amir a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers papa, l'adulte. Tu as soufflé. Bravo. Tu es venu vers papa. Je suis en colère. C'est dit. Les mains restent loin. C'est bien. Tu as soufflé trois fois. Puis je suis venu vers papa. Nino pose un cube dans le panier. Le bois fait un petit bruit. Plus tard, une petite tour. Le cube jaune attend.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,10 +1731,27 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hugo a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers papa, l'adulte.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Amir a nommé sa colère.
+narrateur|Mains loin.
+narrateur|Il peut s'éloigner.
+narrateur|Il va vers papa, l'adulte.
+papa|Tu as soufflé. Bravo.
+maman|Tu es venu vers papa.
+enfant-m|Je suis en colère. C'est dit.
+papa|Les mains restent loin. C'est bien.
+maman|Tu as soufflé trois fois.
+enfant-m|Puis je suis venu vers papa.
+narrateur|Nino pose un cube dans le panier.
+narrateur|Le bois fait un petit bruit.
+papa|Plus tard, une petite tour.
+narrateur|Le cube jaune attend.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>cubes</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1704,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hugo s'assoit près de papa. Les cubes restent sur le tapis.</t>
+          <t>Amir s'assoit près de papa. Les cubes restent sur le tapis. Tu veux ma main ? Oui, maman. Plus tard, une petite tour. Oui. Tout doux. Tu as nommé. Tu t'es éloigné. On laisse les cubes un moment. Oui. Près du panier. La pluie ralentit. Le tapis est encore doux. La chaussette sèche encore.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1840,10 +1912,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hugo s'assoit près de papa. Les cubes restent sur le tapis.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Amir s'assoit près de papa.
+narrateur|Les cubes restent sur le tapis.
+maman|Tu veux ma main ?
+enfant-m|Oui, maman.
+papa|Plus tard, une petite tour.
+enfant-m|Oui. Tout doux.
+maman|Tu as nommé. Tu t'es éloigné.
+papa|On laisse les cubes un moment.
+enfant-m|Oui. Près du panier.
+narrateur|La pluie ralentit.
+narrateur|Le tapis est encore doux.
+narrateur|La chaussette sèche encore.</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>pluie</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1868,7 +1955,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais en colère. Je suis allé vers papa. Tes mains étaient loin. Bravo. La pluie est plus calme. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2008,7 +2095,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'étais en colère. Je suis allé vers papa.
+papa|Tes mains étaient loin. Bravo.
+maman|La pluie est plus calme.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2030,7 +2120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2068,6 +2158,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-01.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo construit une tour de cubes. Il est dans le salon, avec papa. Son frère Nino prend le cube du haut. La tour tombe sur le tapis. Hugo sent son visage chaud. Son ventre est dur. Hugo dit : je suis en &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt;. Il ouvre les doigts. Ses mains restent loin de Nino. Hugo fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Puis il va vers papa. Papa est l'adulte dans le salon. Hugo dit : papa, je suis en colère. Papa écoute. Plus tard, ils reconstruiront. La colère a un nom. Les mains restent loin.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La pluie tapote la vitre. Le tapis a des losanges bleus. Un panier de cubes attend. Les cubes sentent le bois. Le canapé est tout mou. Un cube jaune brille un peu. Une chaussette sèche près du radiateur. La pluie fait un petit bruit. Amir, tu prends le panier ? Oui. Je fais une tour. Nino s'assoit près du tapis. En ce moment, Amir construit une tour. La tour est haute. Nino prend le cube du haut. La tour tombe sur le tapis. Amir sent son visage chaud. Son ventre est dur. Je suis en colère. Il ouvre les doigts. Ses mains restent loin de Nino. Les mains restent loin. Amir fait un pas en arrière. Il peut s'éloigner. Il s'éloigne vers le canapé. Il souffle trois fois. Tu as soufflé. Bravo. Tu peux venir vers moi. Amir va vers papa. Papa est l'adulte dans le salon. Papa, je suis en colère. Je t'écoute. La tour est tombée. Tu as nommé. Tes mains sont loin. Plus tard, on reconstruira. Nino pose le cube dans le panier. Le bois fait un petit bruit. Tu t'es éloigné. C'est bien. Les mains restent loin. On va vers un adulte. La colère a un nom. Les mains restent loin. La pluie tapote encore. Les losanges bleus restent calmes.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hugo est en &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt;. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir est en colère. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1562,7 +1562,6 @@
 narrateur|Que fait-il ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1592,7 +1591,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo a nommé sa &lt;emphasis level="moderate"&gt;colère&lt;/emphasis&gt;. Mains loin. Il peut s'éloigner. Il va vers papa, l'adulte.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir a nommé sa colère. Mains loin. Il peut s'éloigner. Il va vers papa, l'adulte. Tu as soufflé. Bravo. Tu es venu vers papa. Je suis en colère. C'est dit. Les mains restent loin. C'est bien. Tu as soufflé trois fois. Puis je suis venu vers papa. Nino pose un cube dans le panier. Le bois fait un petit bruit. Plus tard, une petite tour. Le cube jaune attend.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1781,7 +1780,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugo s'assoit près de papa. Les cubes restent sur le tapis.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Amir s'assoit près de papa. Les cubes restent sur le tapis. Tu veux ma main ? Oui, maman. Plus tard, une petite tour. Oui. Tout doux. Tu as nommé. Tu t'es éloigné. On laisse les cubes un moment. Oui. Près du panier. La pluie ralentit. Le tapis est encore doux. La chaussette sèche encore.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1955,12 +1954,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais en colère. Je suis allé vers papa. Tes mains étaient loin. Bravo. La pluie est plus calme. L'histoire est finie.</t>
+          <t>J'étais en colère. Je suis allé vers papa. Tes mains étaient loin. Bravo. La pluie est plus calme.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais en colère. Je suis allé vers papa. Tes mains étaient loin. Bravo. La pluie est plus calme.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2097,11 +2096,9 @@
         <is>
           <t>enfant-m|J'étais en colère. Je suis allé vers papa.
 papa|Tes mains étaient loin. Bravo.
-maman|La pluie est plus calme.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|La pluie est plus calme.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2120,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2165,6 +2162,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.005-01.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.005-01.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison</t>
+          <t>maison, salon</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hugo, Nino, papa</t>
+          <t>Amir, Nino, papa, maman</t>
         </is>
       </c>
     </row>
